--- a/meds.xlsx
+++ b/meds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LONG\Desktop\1小兒藥水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA37C19-8B69-477C-9352-374C9365BD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE36EAC-1F61-41EE-A6C3-81E7D27B61A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="-90" windowWidth="15707" windowHeight="9437" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Location</t>
   </si>
@@ -100,13 +100,28 @@
   </si>
   <si>
     <t>L05_Logic</t>
+  </si>
+  <si>
+    <t>L03</t>
+  </si>
+  <si>
+    <t>L03_Logic</t>
+  </si>
+  <si>
+    <t>Curam 312.5mg/5ml</t>
+  </si>
+  <si>
+    <t>諾快寧口服懸液</t>
+  </si>
+  <si>
+    <t>腎功能不全者需調整劑量。使用前請振盪均勻。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,30 +150,11 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2B2D31"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2B2D31"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF2B2D31"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF2B2D31"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -187,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -195,18 +191,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -487,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="14.4140625" customWidth="1"/>
@@ -548,37 +533,61 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="34.75" x14ac:dyDescent="0.75">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/meds.xlsx
+++ b/meds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LONG\Desktop\1小兒藥水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE36EAC-1F61-41EE-A6C3-81E7D27B61A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F7EAB-F7F9-4C15-B49A-4C46F3F8CEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="-90" windowWidth="15707" windowHeight="9437" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Location</t>
   </si>
@@ -115,13 +115,45 @@
   </si>
   <si>
     <t>腎功能不全者需調整劑量。使用前請振盪均勻。</t>
+  </si>
+  <si>
+    <t>L06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L06_Logic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L07</t>
+  </si>
+  <si>
+    <t>Peace solution 60mL</t>
+  </si>
+  <si>
+    <t>鼻解糖漿</t>
+  </si>
+  <si>
+    <t>此藥含有抗組織胺及去鼻塞成分。</t>
+  </si>
+  <si>
+    <t>L07_Logic</t>
+  </si>
+  <si>
+    <t>Ibuprofen Suspension 20mg/mL</t>
+  </si>
+  <si>
+    <t>舒抑痛 (Idofen)</t>
+  </si>
+  <si>
+    <t>飯後服用。使用前請振盪均勻。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,23 +170,16 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF2B2D31"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF2B2D31"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -191,7 +216,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -472,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="14.4140625" customWidth="1"/>
@@ -482,7 +507,7 @@
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.15" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" ht="28.3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -516,7 +541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="25.75" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -533,24 +558,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
+      <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -574,7 +599,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" ht="38.6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -589,6 +614,40 @@
       </c>
       <c r="E7" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/meds.xlsx
+++ b/meds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LONG\Desktop\1小兒藥水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F7EAB-F7F9-4C15-B49A-4C46F3F8CEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9CF897-2AAA-4853-804E-B0C93141DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="-90" windowWidth="15707" windowHeight="9437" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="2400" windowWidth="12343" windowHeight="6227" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>Location</t>
   </si>
@@ -147,6 +147,183 @@
   </si>
   <si>
     <t>飯後服用。使用前請振盪均勻。</t>
+  </si>
+  <si>
+    <t>L08</t>
+  </si>
+  <si>
+    <t>Procaterol Liquid 300mcg/60mL</t>
+  </si>
+  <si>
+    <t>喘解液</t>
+  </si>
+  <si>
+    <t>使用後可能會有心悸或手抖副作用。</t>
+  </si>
+  <si>
+    <t>L08_Logic</t>
+  </si>
+  <si>
+    <t>L09</t>
+  </si>
+  <si>
+    <t>Mintapp 1mg/mL</t>
+  </si>
+  <si>
+    <t>敏達糖漿</t>
+  </si>
+  <si>
+    <t>此藥為長效抗組織胺，較不易嗜睡。</t>
+  </si>
+  <si>
+    <t>L09_Logic</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <t>Wempty suspension 1mg/mL</t>
+  </si>
+  <si>
+    <t>胃利空口服懸液</t>
+  </si>
+  <si>
+    <t>飯前 15-30 分鐘服用。使用前請振盪均勻。</t>
+  </si>
+  <si>
+    <t>L10_Logic</t>
+  </si>
+  <si>
+    <t>L11</t>
+  </si>
+  <si>
+    <t>Ulexin suspension 25mg/mL</t>
+  </si>
+  <si>
+    <t>優力黴素口服懸液</t>
+  </si>
+  <si>
+    <t>泡好後需冷藏，使用前請振盪均勻。</t>
+  </si>
+  <si>
+    <t>L11_Logic</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <t>Ventol solution 5.34mg/mL</t>
+  </si>
+  <si>
+    <t>舒喘內服液</t>
+  </si>
+  <si>
+    <t>劑量需依血中濃度個別化調整。肥胖者應以理想體重計算。</t>
+  </si>
+  <si>
+    <t>L13_Logic</t>
+  </si>
+  <si>
+    <t>L16</t>
+  </si>
+  <si>
+    <t>Kidsolone 1mg/mL, 60mL</t>
+  </si>
+  <si>
+    <t>必爾生口服液</t>
+  </si>
+  <si>
+    <t>劑量隨病情調整。長期使用建議早晨服用。</t>
+  </si>
+  <si>
+    <t>L16_Logic</t>
+  </si>
+  <si>
+    <t>L18</t>
+  </si>
+  <si>
+    <t>Keppra oral solution 100mg/mL</t>
+  </si>
+  <si>
+    <t>優閒內服液劑</t>
+  </si>
+  <si>
+    <t>體重≤20kg建議使用此液劑。開瓶後請依說明書保存。</t>
+  </si>
+  <si>
+    <t>L18_Logic</t>
+  </si>
+  <si>
+    <t>L904</t>
+  </si>
+  <si>
+    <t>Seridol oral solution 1mg/mL</t>
+  </si>
+  <si>
+    <t>賽力多內服液劑</t>
+  </si>
+  <si>
+    <t>滴定期間需密切觀察嗜睡、體重增加等副作用。</t>
+  </si>
+  <si>
+    <t>L904_Logic</t>
+  </si>
+  <si>
+    <t>L911</t>
+  </si>
+  <si>
+    <t>Mycostatin oral Suspension</t>
+  </si>
+  <si>
+    <t>滅菌靈懸液用粉劑</t>
+  </si>
+  <si>
+    <t>兩邊口腔各滴一半。漱口含住再吞下效果更好。</t>
+  </si>
+  <si>
+    <t>L911_Logic</t>
+  </si>
+  <si>
+    <t>L908</t>
+  </si>
+  <si>
+    <t>Trileptal oral suspension 60mg/mL</t>
+  </si>
+  <si>
+    <t>除癲達口服懸浮液</t>
+  </si>
+  <si>
+    <t>此懸浮液不可與緩釋錠劑互換。使用前請充分振盪。</t>
+  </si>
+  <si>
+    <t>L908_Logic</t>
+  </si>
+  <si>
+    <t>L912</t>
+  </si>
+  <si>
+    <t>Depakine oral solution 200mg/mL</t>
+  </si>
+  <si>
+    <t>帝拔癲口服液</t>
+  </si>
+  <si>
+    <t>濃度極高，請精確量取。2歲以下有肝毒性風險。</t>
+  </si>
+  <si>
+    <t>L912_Logic</t>
+  </si>
+  <si>
+    <t>L915</t>
+  </si>
+  <si>
+    <t>Levim oral solution 100mg/mL</t>
+  </si>
+  <si>
+    <t>樂閒內服液劑</t>
+  </si>
+  <si>
+    <t>避免突然停藥。體重≤20kg建議使用此液劑。</t>
   </si>
 </sst>
 </file>
@@ -497,12 +674,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="14.4140625" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.08203125" customWidth="1"/>
+    <col min="2" max="3" width="38.875" customWidth="1"/>
     <col min="4" max="4" width="16.58203125" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
   </cols>
@@ -650,6 +826,207 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/meds.xlsx
+++ b/meds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LONG\Desktop\1小兒藥水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9CF897-2AAA-4853-804E-B0C93141DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8406D8E-D1C5-4D0B-8073-DBFBF927AB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="2400" windowWidth="12343" windowHeight="6227" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="-90" windowWidth="15707" windowHeight="9437" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>Location</t>
   </si>
@@ -324,13 +324,16 @@
   </si>
   <si>
     <t>避免突然停藥。體重≤20kg建議使用此液劑。</t>
+  </si>
+  <si>
+    <t>L915_Logic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +360,19 @@
       <color rgb="FF2B2D31"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2B2D31"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -385,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -393,7 +409,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -769,262 +790,265 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
-      <c r="A7" s="1" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="61.75" x14ac:dyDescent="0.75">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="41.8" x14ac:dyDescent="0.75">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:5" ht="61.75" x14ac:dyDescent="0.75">
+      <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
+    <row r="11" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
+    <row r="12" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
+    <row r="13" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
+    <row r="14" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A15" t="s">
+    <row r="15" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
+    <row r="16" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
+    <row r="17" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
+    <row r="18" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
+    <row r="19" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
+    <row r="20" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
+    <row r="21" spans="1:5" ht="16.3" x14ac:dyDescent="0.85">
+      <c r="A21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="5" t="s">
         <v>98</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
